--- a/outputs/Collision_metrics_reproducibility.xlsx
+++ b/outputs/Collision_metrics_reproducibility.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2279,6 +2279,218 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>1988_Davies</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Davies</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>A review of information relating to fish passage through turbines: Implications to tidal power schemes. Journa</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>turbine-passage injury mechanisms (incl. blade strike)</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>1997_Cada</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Cada</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Shaken, not stirred: the recipe for a fish-friendly turbine</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>biological design criteria (blade strike)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2000_Bickford</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Bickford</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Reanalysis and Interpretation of 25 years of Snake-Columbia River Juvenile Salmon Survival Studies. North Amer</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>turbine-passage survival reanalysis</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2002_Skalski</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Skalski</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Effects of turbine operating efficiency on smolt passage survival</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>turbine-efficiency vs survival reanalysis</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2007_Jansen</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Jansen</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Survival and movement of fish experimentally passed through a re-runnered turbine at the Kelsey Generating Station</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>live-fish field</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>survival; injury/condition (HI-Z balloon-tag)</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2023_Koukouvinis</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Koukouvinis</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>State of the Art in Designing Fish-Friendly Turbines - Concepts and Performance Indicators</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>fish-friendly turbine design / CFD (blade strike)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2291,7 +2503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4611,6 +4823,98 @@
       <c r="R25" s="2" t="inlineStr">
         <is>
           <t>strike probability; strike velocity; blade/leading-edge geometry (L/t)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2007_Jansen</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Jansen</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Survival and movement of fish experimentally passed through a re-runnered turbine at the Kelsey Generating Station</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>survival probability (HI-Z paired release-recapture); injury/condition</t>
         </is>
       </c>
     </row>
